--- a/vault-dalarna-university/02 IHV/Analys/Innehåll.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Innehåll.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Innehåll" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH32Z</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (807 tecken): Verksamhetsförlagt projekt (VFP) inom idrottstränarprogrammet utförs i en organisation som verkar inom området idrott, f…</t>
+          <t>Osannolikt kort (62 tecken): 'Betyg och bedömningsfrågor knutna till ämnet idrott och hälsa.'</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH32Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (830 tecken): Entreprenörskap inom området idrott och hälsa sätts i ett nationellt, internationellt och globalt perspektiv. I kursen f…</t>
+          <t>5 meningar i ett stycke (807 tecken): Verksamhetsförlagt projekt (VFP) inom idrottstränarprogrammet utförs i en organisation som verkar inom området idrott, f…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (581 tecken): Kursen belyser de yttre krafter som påverkar en idrottare under fysisk aktivitet. Vidare så studeras vilken inre muskelk…</t>
+          <t>5 meningar i ett stycke (830 tecken): Entreprenörskap inom området idrott och hälsa sätts i ett nationellt, internationellt och globalt perspektiv. I kursen f…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (534 tecken): Studenten möter metoder för datainsamling samt grundläggande och fördjupande kvalitativa och kvantitativa insamlingsmeto…</t>
+          <t>4 meningar i ett stycke (581 tecken): Kursen belyser de yttre krafter som påverkar en idrottare under fysisk aktivitet. Vidare så studeras vilken inre muskelk…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (421 tecken): Kursen omfattar såväl teoretisk som tillämpad strategisk medieplanering för både traditionella och nya medier. Kursen in…</t>
+          <t>4 meningar i ett stycke (534 tecken): Studenten möter metoder för datainsamling samt grundläggande och fördjupande kvalitativa och kvantitativa insamlingsmeto…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (513 tecken): I kursen utforskas olika möjligheter att röra sig till musikens puls, rytm och karaktär. Den studerande får skapa och ge…</t>
+          <t>5 meningar i ett stycke (421 tecken): Kursen omfattar såväl teoretisk som tillämpad strategisk medieplanering för både traditionella och nya medier. Kursen in…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH39C</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1113,14 +1113,14 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH39C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (922 tecken): I kursen behandlas teoretiska och praktiska metoder för att planera, genomföra och utvärdera styrketräning för tävlingsi…</t>
+          <t>4 meningar i ett stycke (513 tecken): I kursen utforskas olika möjligheter att röra sig till musikens puls, rytm och karaktär. Den studerande får skapa och ge…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39C</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH39F</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1358 tecken): Kursen syftar till att den studerande utvecklar sina teoretiska kunskaper inom kunskapsområdet träningsvetenskap och sin…</t>
+          <t>Osannolikt kort (62 tecken): 'Betyg och bedömningsfrågor knutna till ämnet idrott och hälsa.'</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1298 tecken): Kursen syftar till att den studerande utvecklar sina teoretiska kunskaper inom kunskapsområdet träningsvetenskap och sin…</t>
+          <t>7 meningar i ett stycke (922 tecken): I kursen behandlas teoretiska och praktiska metoder för att planera, genomföra och utvärdera styrketräning för tävlingsi…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (605 tecken): I kursen studeras människans energi- och näringsbehov utifrån makronutrienterna och de mest centrala mikronutrienternas …</t>
+          <t>9 meningar i ett stycke (1358 tecken): Kursen syftar till att den studerande utvecklar sina teoretiska kunskaper inom kunskapsområdet träningsvetenskap och sin…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (892 tecken): Denna kurs i idrottspsykologi syftar till att ge studenten en praktisk och teoretisk förståelse för hur psykologiska ver…</t>
+          <t>9 meningar i ett stycke (1298 tecken): Kursen syftar till att den studerande utvecklar sina teoretiska kunskaper inom kunskapsområdet träningsvetenskap och sin…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH3F9</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (637 tecken): I kursen diskuteras olika aspekter av idrottsledarskapet i relation till ekologisk, social och ekonomisk hållbarhet samt…</t>
+          <t>5 meningar i ett stycke (605 tecken): I kursen studeras människans energi- och näringsbehov utifrån makronutrienterna och de mest centrala mikronutrienternas …</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH3FF</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (632 tecken): I denna kurs studeras de fysiologiska systemen som har betydelse för fysisk aktivitet och idrottslig prestationsförmåga.…</t>
+          <t>5 meningar i ett stycke (892 tecken): Denna kurs i idrottspsykologi syftar till att ge studenten en praktisk och teoretisk förståelse för hur psykologiska ver…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH3G7</t>
+          <t>GIH3F9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (606 tecken): Kursen behandlar planering för, och genomförande av, olika metoder för analys av tekniska, taktiska och/eller fysiologis…</t>
+          <t>4 meningar i ett stycke (637 tecken): I kursen diskuteras olika aspekter av idrottsledarskapet i relation till ekologisk, social och ekonomisk hållbarhet samt…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3FF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (707 tecken): Denna kurs ger studenterna en praktisk inblick i vad tränarrollen innebär samt utrustar studenterna med verktyg för att …</t>
+          <t>4 meningar i ett stycke (632 tecken): I denna kurs studeras de fysiologiska systemen som har betydelse för fysisk aktivitet och idrottslig prestationsförmåga.…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (570 tecken): I kursen fördjupas kunskapen om företagande och om den kreativa processen att utveckla en affärsidé utifrån gällande for…</t>
+          <t>4 meningar i ett stycke (606 tecken): Kursen behandlar planering för, och genomförande av, olika metoder för analys av tekniska, taktiska och/eller fysiologis…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (539 tecken): I kursen behandlas grundläggande principer inom näringslära inklusive människans energi- och näringsbehov. I kursen stud…</t>
+          <t>4 meningar i ett stycke (707 tecken): Denna kurs ger studenterna en praktisk inblick i vad tränarrollen innebär samt utrustar studenterna med verktyg för att …</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH3GD</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (892 tecken): Denna kurs i idrottspsykologi syftar till att ge studenten en praktisk och teoretisk förståelse för hur psykologiska ver…</t>
+          <t>4 meningar i ett stycke (570 tecken): I kursen fördjupas kunskapen om företagande och om den kreativa processen att utveckla en affärsidé utifrån gällande for…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (533 tecken): I denna kurs studeras de fysiologiska systemen som har betydelse för fysisk aktivitet och idrottslig prestationsförmåga.…</t>
+          <t>4 meningar i ett stycke (539 tecken): I kursen behandlas grundläggande principer inom näringslära inklusive människans energi- och näringsbehov. I kursen stud…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IH1009</t>
+          <t>GIH3GD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (696 tecken): I kursen belyses frågor kring rörelsens betydelse och möjligheter till delaktighet för alla barn och ungdomar. Vidare st…</t>
+          <t>5 meningar i ett stycke (892 tecken): Denna kurs i idrottspsykologi syftar till att ge studenten en praktisk och teoretisk förståelse för hur psykologiska ver…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>GIH3JL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (476 tecken): I kursen introduceras några socialpsykologiska teorier om individer och grupper. Med dessa teorier som grund granskas oc…</t>
+          <t>4 meningar i ett stycke (533 tecken): I denna kurs studeras de fysiologiska systemen som har betydelse för fysisk aktivitet och idrottslig prestationsförmåga.…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IH1025</t>
+          <t>IH1009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (630 tecken): I kursen behandlas begreppen testers validitet och reliabilitet. Därutöver belyses testers roll för optimering av hälsoa…</t>
+          <t>5 meningar i ett stycke (696 tecken): I kursen belyses frågor kring rörelsens betydelse och möjligheter till delaktighet för alla barn och ungdomar. Vidare st…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (505 tecken): I kursen behandlas idrottsmedicinska grunder såsom förberedelse och träning, förebyggande av skador, diagnos och behandl…</t>
+          <t>5 meningar i ett stycke (476 tecken): I kursen introduceras några socialpsykologiska teorier om individer och grupper. Med dessa teorier som grund granskas oc…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>IH1025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (625 tecken): I kursen behandlas grundläggande kunskaper om och vissa färdigheter i åldersanpassad träning med specifik inriktning mot…</t>
+          <t>7 meningar i ett stycke (630 tecken): I kursen behandlas begreppen testers validitet och reliabilitet. Därutöver belyses testers roll för optimering av hälsoa…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (990 tecken): I kursen studeras grundläggande kunskaper om näringsbehov och rekommendationer vid fysisk aktivitet på olika nivåer. Kur…</t>
+          <t>4 meningar i ett stycke (505 tecken): I kursen behandlas idrottsmedicinska grunder såsom förberedelse och träning, förebyggande av skador, diagnos och behandl…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1202 tecken): I kursen studeras människokroppens uppbyggnad och dess funktion i förhållande till idrott och fysisk aktivitet. Särskild…</t>
+          <t>Osannolikt kort (70 tecken): 'I kursen behandlas hur strategiska nätverk och partnerskap kan byggas.'</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IH2003</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (428 tecken): I kursen behandlas kunskaper och färdigheter inom kunskapsområdet vinterfriluftsliv. Stor vikt läggs vid didaktiska fråg…</t>
+          <t>Osannolikt kort (75 tecken): 'Kursen behandlar produktutvecklingsprocessen utifrån aktuell teoribildning.'</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IH2004</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (605 tecken): I kursen studeras och problematiseras begreppet och fenomenet hälsa. Hälsa och arbetsmiljö diskuteras ur olika didaktisk…</t>
+          <t>4 meningar i ett stycke (625 tecken): I kursen behandlas grundläggande kunskaper om och vissa färdigheter i åldersanpassad träning med specifik inriktning mot…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (702 tecken): I kursen behandlas ett brett spektrum av olika former av rörelser till musik som kan användas i pedagogisk verksamhet. I…</t>
+          <t>7 meningar i ett stycke (990 tecken): I kursen studeras grundläggande kunskaper om näringsbehov och rekommendationer vid fysisk aktivitet på olika nivåer. Kur…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IH2006</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (608 tecken): I kursen analyseras och värderas olika idrotts- och motionsaktiviteter ur ett humanbiologiskt och vetenskapligt perspekt…</t>
+          <t>8 meningar i ett stycke (1202 tecken): I kursen studeras människokroppens uppbyggnad och dess funktion i förhållande till idrott och fysisk aktivitet. Särskild…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>IH2003</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (716 tecken): Under kursen studeras smärtupplevelsen och uppkomstmekanismer bakom olika smärttillstånd, liksom hur smärta kan diagnost…</t>
+          <t>5 meningar i ett stycke (428 tecken): I kursen behandlas kunskaper och färdigheter inom kunskapsområdet vinterfriluftsliv. Stor vikt läggs vid didaktiska fråg…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>IH2004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (549 tecken): Kursen fokuserar på personcentrerad vård vid astma, KOL och allergi. I kursen studeras bland annat risker, orsaker och p…</t>
+          <t>6 meningar i ett stycke (605 tecken): I kursen studeras och problematiseras begreppet och fenomenet hälsa. Hälsa och arbetsmiljö diskuteras ur olika didaktisk…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (490 tecken): I kursen studeras farmakologiska behandlingsprinciper vid diabetes (typ-1 och typ-2) samt vid till exempel hypertoni, is…</t>
+          <t>6 meningar i ett stycke (702 tecken): I kursen behandlas ett brett spektrum av olika former av rörelser till musik som kan användas i pedagogisk verksamhet. I…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>IH2006</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (932 tecken): Under kursen studeras sambanden mellan fysisk aktivitet och hälsa. Såväl kardiovaskulära, metabola, hormonella, immunolo…</t>
+          <t>6 meningar i ett stycke (608 tecken): I kursen analyseras och värderas olika idrotts- och motionsaktiviteter ur ett humanbiologiskt och vetenskapligt perspekt…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (769 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
+          <t>4 meningar i ett stycke (716 tecken): Under kursen studeras smärtupplevelsen och uppkomstmekanismer bakom olika smärttillstånd, liksom hur smärta kan diagnost…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (794 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
+          <t>6 meningar i ett stycke (549 tecken): Kursen fokuserar på personcentrerad vård vid astma, KOL och allergi. I kursen studeras bland annat risker, orsaker och p…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (579 tecken): I kursen studeras matspjälkning och näringshantering, rörelseapparaten, nervsystemet, hormonella system, urinvägssysteme…</t>
+          <t>4 meningar i ett stycke (490 tecken): I kursen studeras farmakologiska behandlingsprinciper vid diabetes (typ-1 och typ-2) samt vid till exempel hypertoni, is…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (636 tecken): I kursen studeras allmän farmakologi vad gäller dynamik, kinetik, interaktioner, biverkningar och variationer i läkemede…</t>
+          <t>5 meningar i ett stycke (932 tecken): Under kursen studeras sambanden mellan fysisk aktivitet och hälsa. Såväl kardiovaskulära, metabola, hormonella, immunolo…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (433 tecken): I kursen studeras allmän farmakologi vad gäller dynamik, kinetik, interaktioner, biverkningar och variationer i läkemede…</t>
+          <t>7 meningar i ett stycke (769 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (990 tecken): I kursen studeras grundläggande psykiatriska begrepp, de diagnostiska system som psykiatrin vilar på och innebörden av "…</t>
+          <t>7 meningar i ett stycke (794 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (769 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
+          <t>4 meningar i ett stycke (579 tecken): I kursen studeras matspjälkning och näringshantering, rörelseapparaten, nervsystemet, hormonella system, urinvägssysteme…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (813 tecken): Kursen behandlar några av naturens olika kretslopp och ekologiska samband med utgångspunkt i förskolans närmiljö för att…</t>
+          <t>6 meningar i ett stycke (636 tecken): I kursen studeras allmän farmakologi vad gäller dynamik, kinetik, interaktioner, biverkningar och variationer i läkemede…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (650 tecken): I kursen behandlas teknik utifrån elevnära exempel hämtade från vardag och samhälle. Övergripande studeras teknikutveckl…</t>
+          <t>4 meningar i ett stycke (433 tecken): I kursen studeras allmän farmakologi vad gäller dynamik, kinetik, interaktioner, biverkningar och variationer i läkemede…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>NV1027</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (849 tecken): I kursen behandlas hållbar utveckling ur ett ekologiskt, ekonomiskt samt socialt perspektiv, med särskilt fokus på ekolo…</t>
+          <t>8 meningar i ett stycke (990 tecken): I kursen studeras grundläggande psykiatriska begrepp, de diagnostiska system som psykiatrin vilar på och innebörden av "…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (880 tecken): Kursen behandlar begreppet hållbar utveckling och möjligheterna att skapa levnadsvillkor och använda resurser på ett sät…</t>
+          <t>7 meningar i ett stycke (769 tecken): I kursen studeras farmakodynamik, farmakokinetik, läkemedelsrespons, läkemedlens påverkan på miljön och läkemedelsintera…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (476 tecken): Kursen fokuserar på personer med funktionsnedsättning ur ett brukar-, samhälls- och delaktighetsperspektiv. Levnadsvillk…</t>
+          <t>5 meningar i ett stycke (813 tecken): Kursen behandlar några av naturens olika kretslopp och ekologiska samband med utgångspunkt i förskolans närmiljö för att…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (478 tecken): Kursen behandlar elevhälsopersonalens roll, kompetens och yrkesområde som delaktig i arbetet för att förebygga, fånga up…</t>
+          <t>7 meningar i ett stycke (650 tecken): I kursen behandlas teknik utifrån elevnära exempel hämtade från vardag och samhälle. Övergripande studeras teknikutveckl…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>NV1027</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (515 tecken): I kursen studeras och behandlas historik, grunder och förhållningssätt inom kognitiv beteendeterapi. Betoningen i kursen…</t>
+          <t>7 meningar i ett stycke (849 tecken): I kursen behandlas hållbar utveckling ur ett ekologiskt, ekonomiskt samt socialt perspektiv, med särskilt fokus på ekolo…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (559 tecken): Kursen introducerar den studerande i svensk och internationell socialpolitik utifrån centrala socialpolitiska begrepp oc…</t>
+          <t>4 meningar i ett stycke (880 tecken): Kursen behandlar begreppet hållbar utveckling och möjligheterna att skapa levnadsvillkor och använda resurser på ett sät…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (703 tecken): Kursen är en grundläggande kurs om samsjuklighet i form av skadligt bruk eller beroende avseende alkohol, narkotika elle…</t>
+          <t>4 meningar i ett stycke (476 tecken): Kursen fokuserar på personer med funktionsnedsättning ur ett brukar-, samhälls- och delaktighetsperspektiv. Levnadsvillk…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (510 tecken): Kursen behandlar teoretiska och praktiska kunskaper i socialt arbete rörande försörjning, rehabilitering och aktivering …</t>
+          <t>4 meningar i ett stycke (478 tecken): Kursen behandlar elevhälsopersonalens roll, kompetens och yrkesområde som delaktig i arbetet för att förebygga, fånga up…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,51 +2350,51 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (588 tecken): Kursen är en introduktion till socialt arbete som profession. Kursen behandlar grundläggande frågor av betydelse för utv…</t>
+          <t>4 meningar i ett stycke (515 tecken): I kursen studeras och behandlas historik, grunder och förhållningssätt inom kognitiv beteendeterapi. Betoningen i kursen…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (528 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
+          <t>Osannolikt kort (55 tecken): '**Moment 1. Campusförlagd utbildning, 5 högskolepoäng**'</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (528 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
+          <t>5 meningar i ett stycke (559 tecken): Kursen introducerar den studerande i svensk och internationell socialpolitik utifrån centrala socialpolitiska begrepp oc…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
+          <t>5 meningar i ett stycke (703 tecken): Kursen är en grundläggande kurs om samsjuklighet i form av skadligt bruk eller beroende avseende alkohol, narkotika elle…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (431 tecken): I kursen ingår att planera, genomföra och sammanställa en vetenskaplig undersökning inom sexuell, reproduktiv och perina…</t>
+          <t>4 meningar i ett stycke (510 tecken): Kursen behandlar teoretiska och praktiska kunskaper i socialt arbete rörande försörjning, rehabilitering och aktivering …</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (535 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
+          <t>4 meningar i ett stycke (588 tecken): Kursen är en introduktion till socialt arbete som profession. Kursen behandlar grundläggande frågor av betydelse för utv…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
+          <t>4 meningar i ett stycke (528 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ASR2B9</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (548 tecken): Studenterna kommer att studera evidensbaserad mödra- och nyföddhetsvård ur ett globalt och nationellt perspektiv. Releva…</t>
+          <t>4 meningar i ett stycke (528 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2B9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (782 tecken): Kursen omfattar ett holistiskt grepp om ämnet sexuell och reproduktiv hälsa samt rättigheter (SRHR), inklusive hälsofräm…</t>
+          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSR3BZ</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (787 tecken): Kursen omfattar ett holistiskt förhållningssätt i ämnet sexuell och reproduktiv hälsa samt rättigheter (SRHR), inklusive…</t>
+          <t>4 meningar i ett stycke (431 tecken): I kursen ingår att planera, genomföra och sammanställa en vetenskaplig undersökning inom sexuell, reproduktiv och perina…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (447 tecken): I kursen studeras barnmorskans profession och forskningsområde ur ett globalt och nationellt perspektiv. Relevanta polic…</t>
+          <t>4 meningar i ett stycke (535 tecken): Kursen omfattar reflektion, diskussion och problematisering av komplicerade förlopp i samband med handläggning av gravid…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (716 tecken): I kursen studeras barnmorskans profession, yrkesansvar och forskningsområde ur ett historiskt, nationellt och internatio…</t>
+          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>ASR2B9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (616 tecken): Kursen omfattar reflektion, diskussion och problematisering av normala och komplicerade förlopp i samband med handläggni…</t>
+          <t>4 meningar i ett stycke (548 tecken): Studenterna kommer att studera evidensbaserad mödra- och nyföddhetsvård ur ett globalt och nationellt perspektiv. Releva…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2B9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
+          <t>5 meningar i ett stycke (782 tecken): Kursen omfattar ett holistiskt grepp om ämnet sexuell och reproduktiv hälsa samt rättigheter (SRHR), inklusive hälsofräm…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>GSR3BZ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (1016 tecken): Kursen innehåller fördjupad självständig tillämpning och integrering av klinisk och teoretisk kunskap i samband med alla…</t>
+          <t>4 meningar i ett stycke (787 tecken): Kursen omfattar ett holistiskt förhållningssätt i ämnet sexuell och reproduktiv hälsa samt rättigheter (SRHR), inklusive…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1504 tecken): Kursen innehåller självständig tillämpning och integrering av klinisk och teoretisk kunskap i samband med alla moment, u…</t>
+          <t>4 meningar i ett stycke (447 tecken): I kursen studeras barnmorskans profession och forskningsområde ur ett globalt och nationellt perspektiv. Relevanta polic…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GVV3JJ</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (612 tecken): I kursen studeras människokroppens strukturer och funktioner samt vanligt förekommande funktionsnedsättningar med releva…</t>
+          <t>5 meningar i ett stycke (716 tecken): I kursen studeras barnmorskans profession, yrkesansvar och forskningsområde ur ett historiskt, nationellt och internatio…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GVV3JK</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (628 tecken): Kursen behandlar grundläggande biomekanik, olika mät- och skattningsmetoder samt mätteknisk utrustning med relevans för …</t>
+          <t>4 meningar i ett stycke (616 tecken): Kursen omfattar reflektion, diskussion och problematisering av normala och komplicerade förlopp i samband med handläggni…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>VV2001</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (532 tecken): I kursen diskuteras det specifika för barnmorskans yrkesområde med fokus på handledningssituationen. Barnmorskans kompet…</t>
+          <t>5 meningar i ett stycke (787 tecken): Kursen innehåller tillämpning, fördjupning och integrering av klinisk och teoretisk kunskap i samband med vård av kvinno…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (738 tecken): I kursen studeras sexuell och reproduktiv hälsa samt barnmorskans profession ur ett historiskt, nationellt och internati…</t>
+          <t>6 meningar i ett stycke (1016 tecken): Kursen innehåller fördjupad självständig tillämpning och integrering av klinisk och teoretisk kunskap i samband med alla…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>VV3007</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,44 +2890,179 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (469 tecken): Kursen omfattar teoretiska grunder för det normala fysiologiska och psykologiska förloppet i samband med graviditet, för…</t>
+          <t>8 meningar i ett stycke (1504 tecken): Kursen innehåller självständig tillämpning och integrering av klinisk och teoretisk kunskap i samband med alla moment, u…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>GVV3JJ</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4 meningar i ett stycke (612 tecken): I kursen studeras människokroppens strukturer och funktioner samt vanligt förekommande funktionsnedsättningar med releva…</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GVV3JK</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>5 meningar i ett stycke (628 tecken): Kursen behandlar grundläggande biomekanik, olika mät- och skattningsmetoder samt mätteknisk utrustning med relevans för …</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>VV2001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5 meningar i ett stycke (532 tecken): I kursen diskuteras det specifika för barnmorskans yrkesområde med fokus på handledningssituationen. Barnmorskans kompet…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>5 meningar i ett stycke (738 tecken): I kursen studeras sexuell och reproduktiv hälsa samt barnmorskans profession ur ett historiskt, nationellt och internati…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>4 meningar i ett stycke (469 tecken): Kursen omfattar teoretiska grunder för det normala fysiologiska och psykologiska förloppet i samband med graviditet, för…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>VV3010</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ostyckad textmassa</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>4 meningar i ett stycke (774 tecken): Kursen innehåller praktisk och teoretisk kunskap i samband med förväntad normal förlossning med friska barn, barn som vå…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E92"/>
+  <autoFilter ref="A1:E97"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3111,6 +3246,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
